--- a/output/pdf_financials_xlsx/CAD.xlsx
+++ b/output/pdf_financials_xlsx/CAD.xlsx
@@ -798,22 +798,22 @@
         <v>0.039256</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.067829</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.019321</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.112683</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.203176</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.215763</v>
       </c>
     </row>
     <row r="13">
@@ -1354,22 +1354,22 @@
         <v>-1.952775</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.21188</v>
+        <v>-3.279709</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.430457</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-9.607075999999999</v>
+        <v>-9.626397000000001</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-8.342711</v>
+        <v>-8.455394</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.574675</v>
+        <v>-5.777851</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-7.123826</v>
+        <v>-7.339589</v>
       </c>
     </row>
     <row r="28">
@@ -1422,22 +1422,22 @@
         <v>-1.952775</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.21188</v>
+        <v>-3.279709</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.430457</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-9.607075999999999</v>
+        <v>-9.626397000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-8.342711</v>
+        <v>-8.455394</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.574675</v>
+        <v>-5.777851</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-7.123826</v>
+        <v>-7.339589</v>
       </c>
     </row>
     <row r="30">
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.090437</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.17759</v>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.08802599999999999</v>
+        <v>2.178463</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>1.265628</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.468211</v>
+        <v>0.377774</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.041206</v>
@@ -4766,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.086551</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.052528</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>0</v>
@@ -4800,10 +4800,10 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.086551</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.052528</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>0</v>
@@ -5599,7 +5599,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -6424,7 +6428,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.2223</v>
       </c>
@@ -6967,7 +6975,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
@@ -9298,7 +9306,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -12309,7 +12321,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">

--- a/output/pdf_financials_xlsx/CAD.xlsx
+++ b/output/pdf_financials_xlsx/CAD.xlsx
@@ -619,31 +619,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.765626</v>
+        <v>0.783626</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.696831</v>
+        <v>0.714831</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.788611</v>
+        <v>0.806611</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.835337</v>
+        <v>0.858337</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.900852</v>
+        <v>0.924852</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.03584</v>
+        <v>1.05984</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.2515</v>
+        <v>1.2755</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.330498</v>
+        <v>1.354498</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.30405</v>
+        <v>1.32605</v>
       </c>
     </row>
     <row r="8">
@@ -4312,10 +4312,10 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006194</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003949</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -4324,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014947</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -4448,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.534579</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -5116,10 +5116,10 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006194</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003949</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014947</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.305481</v>
+        <v>-1.30943</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.369346</v>
@@ -5166,7 +5166,7 @@
         <v>-1.423797</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.673665</v>
+        <v>-1.688612</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-1.814915</v>
@@ -9011,7 +9011,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -10207,7 +10211,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -11236,7 +11244,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -11297,7 +11309,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -11793,7 +11809,11 @@
           <t>Director’s fees 7</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -12855,7 +12875,11 @@
           <t>Director’s fees 9</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -13571,7 +13595,11 @@
           <t>Director’s fees 10</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -14734,7 +14762,11 @@
           <t>Directors’ fees 11</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E165" s="5" t="n">
         <v>0.018</v>
       </c>
